--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/LOUISIANA_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/LOUISIANA_2010.xlsx
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C121">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C342">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C371">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C542">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C612">
